--- a/DULieu.xlsx
+++ b/DULieu.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Thanh\Học AI\TaoApp\QUnLyHSLopCHuNhiem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17BB4E3-989C-4C7D-B3E8-B459AC7695EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8220"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hướng dẫn nạp dữ liệu Excel" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="309">
   <si>
     <t>HoTen</t>
   </si>
@@ -57,12 +58,6 @@
     <t>Nguyễn Thị Kim Anh</t>
   </si>
   <si>
-    <t>Nguyễn Gia Bảo</t>
-  </si>
-  <si>
-    <t>Tống Thị Cẩm Bình</t>
-  </si>
-  <si>
     <t>Phùng Bùi Hồng Chuyên</t>
   </si>
   <si>
@@ -72,15 +67,6 @@
     <t>Nguyễn Thị Ngọc Đang</t>
   </si>
   <si>
-    <t>Lê Minh Đăng</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hào</t>
-  </si>
-  <si>
-    <t>Bùi Thế Hiển</t>
-  </si>
-  <si>
     <t>Hà Ngọc Hơn</t>
   </si>
   <si>
@@ -111,9 +97,6 @@
     <t>Lương Thị Cẩm Liên</t>
   </si>
   <si>
-    <t>Huỳnh Văn Lộc</t>
-  </si>
-  <si>
     <t>Nguyễn Hoàng Nam</t>
   </si>
   <si>
@@ -147,9 +130,6 @@
     <t>Đặng Minh Thái</t>
   </si>
   <si>
-    <t>Lý Phúc Thịnh</t>
-  </si>
-  <si>
     <t>Lê Ngọc Trân</t>
   </si>
   <si>
@@ -159,9 +139,6 @@
     <t>Hàng Minh Ái Thư</t>
   </si>
   <si>
-    <t>Phan Minh Tiến</t>
-  </si>
-  <si>
     <t>Tôn Ngọc Trâm</t>
   </si>
   <si>
@@ -171,12 +148,6 @@
     <t>Nguyễn Lê Tường</t>
   </si>
   <si>
-    <t>Nguyễn Hoàng Vĩnh</t>
-  </si>
-  <si>
-    <t>Bùi Quách Tuấn Vũ</t>
-  </si>
-  <si>
     <t>Phạm Bùi Tường Vy</t>
   </si>
   <si>
@@ -189,12 +160,6 @@
     <t>Nguyễn Văn Trinh</t>
   </si>
   <si>
-    <t>Nguyễn Văn Hiếu</t>
-  </si>
-  <si>
-    <t>Tống Văn Tươi</t>
-  </si>
-  <si>
     <t>Phùng Ngọc Tấn</t>
   </si>
   <si>
@@ -204,15 +169,6 @@
     <t>Nguyễn Văn Hận</t>
   </si>
   <si>
-    <t>Lê Văn Đằng</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Phúc</t>
-  </si>
-  <si>
-    <t>Bùi Hữu Vinh</t>
-  </si>
-  <si>
     <t>Hà Hoàng Nam</t>
   </si>
   <si>
@@ -240,9 +196,6 @@
     <t>Lương Văn Lợi</t>
   </si>
   <si>
-    <t>Huỳnh Văn An</t>
-  </si>
-  <si>
     <t>Nguyễn Hữu Lộc</t>
   </si>
   <si>
@@ -273,18 +226,12 @@
     <t>Đặng Minh Tâm</t>
   </si>
   <si>
-    <t>Lý Văn Vẹn</t>
-  </si>
-  <si>
     <t>Lê Hữu Phương</t>
   </si>
   <si>
     <t>Hàng Minh Trọng</t>
   </si>
   <si>
-    <t>Phan Hùng Cường</t>
-  </si>
-  <si>
     <t>Tôn Văn Bằng</t>
   </si>
   <si>
@@ -294,12 +241,6 @@
     <t>Nguyễn Phước Huệ</t>
   </si>
   <si>
-    <t>Nguyễn Châu Um</t>
-  </si>
-  <si>
-    <t>Bùi Văn Thì</t>
-  </si>
-  <si>
     <t>Phạm Tấn Tài</t>
   </si>
   <si>
@@ -312,12 +253,6 @@
     <t>Lê Thị Mỹ Hậu</t>
   </si>
   <si>
-    <t>Nguyễn Thị  Thanh Huệ</t>
-  </si>
-  <si>
-    <t>Trần Thị Bền</t>
-  </si>
-  <si>
     <t>Bùi Thị Bích Vân</t>
   </si>
   <si>
@@ -327,15 +262,6 @@
     <t>Trần Thị Minh Lý</t>
   </si>
   <si>
-    <t>Cao Thị Phụng</t>
-  </si>
-  <si>
-    <t>Phan Thị Oanh</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Cẩm Em</t>
-  </si>
-  <si>
     <t>Lê Thị Nga</t>
   </si>
   <si>
@@ -363,9 +289,6 @@
     <t>Võ Thị Giáp</t>
   </si>
   <si>
-    <t>Lê Thị Loan</t>
-  </si>
-  <si>
     <t>Nguyễn Thị Diễm</t>
   </si>
   <si>
@@ -399,18 +322,12 @@
     <t>Lê Thị Kim Thâu</t>
   </si>
   <si>
-    <t>Phan Thị Dòn</t>
-  </si>
-  <si>
     <t>Nguyễn Thị Chen</t>
   </si>
   <si>
     <t>Hồ Thị Thùy Trang</t>
   </si>
   <si>
-    <t>Trương Thị Ngọc Bích</t>
-  </si>
-  <si>
     <t>Lý Thị Kim Châu</t>
   </si>
   <si>
@@ -420,12 +337,6 @@
     <t>Lê Thị Thúy</t>
   </si>
   <si>
-    <t>Nguyễn Thị Tám</t>
-  </si>
-  <si>
-    <t>Quách Thi Tuyền</t>
-  </si>
-  <si>
     <t>Bùi Thị Hồng Nho</t>
   </si>
   <si>
@@ -438,12 +349,6 @@
     <t>377/8 Kiến bình 2</t>
   </si>
   <si>
-    <t>520/19 Long Thượng</t>
-  </si>
-  <si>
-    <t>Kiến Bình 1</t>
-  </si>
-  <si>
     <t>292/10 Long Thượng</t>
   </si>
   <si>
@@ -453,15 +358,6 @@
     <t>355/11, Hoà Hạ</t>
   </si>
   <si>
-    <t>126/5  Phú Thượng 3</t>
-  </si>
-  <si>
-    <t>896/...Kiến Bình 1</t>
-  </si>
-  <si>
-    <t>644/2 Phú Thượng 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">640/24 Kiến Bình 1 </t>
   </si>
   <si>
@@ -492,9 +388,6 @@
     <t>109/5 Kiến bình 1</t>
   </si>
   <si>
-    <t>Hoà Bình</t>
-  </si>
-  <si>
     <t>Kiến Bình 2</t>
   </si>
   <si>
@@ -525,18 +418,12 @@
     <t>488/19 Kiến Bình 1</t>
   </si>
   <si>
-    <t>536/..Long Hạ</t>
-  </si>
-  <si>
     <t>538/19 Phú Hạ 1</t>
   </si>
   <si>
     <t xml:space="preserve">13/1  Long Bình </t>
   </si>
   <si>
-    <t>703/26 phú hạ 2</t>
-  </si>
-  <si>
     <t>137/3 Hòa Hạ</t>
   </si>
   <si>
@@ -546,12 +433,6 @@
     <t>298/3 Phú Thượng 3</t>
   </si>
   <si>
-    <t xml:space="preserve">360/14 Hòa Bình </t>
-  </si>
-  <si>
-    <t xml:space="preserve">574/14 Kiến bình </t>
-  </si>
-  <si>
     <t xml:space="preserve">428/16 Hoà Bình </t>
   </si>
   <si>
@@ -567,12 +448,6 @@
     <t>2201381990</t>
   </si>
   <si>
-    <t>2200348946</t>
-  </si>
-  <si>
-    <t>2201381963</t>
-  </si>
-  <si>
     <t>2108438829</t>
   </si>
   <si>
@@ -582,15 +457,6 @@
     <t>2200377491</t>
   </si>
   <si>
-    <t>2201382042</t>
-  </si>
-  <si>
-    <t>2108438838</t>
-  </si>
-  <si>
-    <t>2200348868</t>
-  </si>
-  <si>
     <t>2201381920</t>
   </si>
   <si>
@@ -621,9 +487,6 @@
     <t>2108438849</t>
   </si>
   <si>
-    <t>2108438911</t>
-  </si>
-  <si>
     <t>2201382002</t>
   </si>
   <si>
@@ -657,9 +520,6 @@
     <t>2108438926</t>
   </si>
   <si>
-    <t>2200348902</t>
-  </si>
-  <si>
     <t>2201382028</t>
   </si>
   <si>
@@ -669,9 +529,6 @@
     <t>2200348882</t>
   </si>
   <si>
-    <t>2108438929</t>
-  </si>
-  <si>
     <t>2200348827</t>
   </si>
   <si>
@@ -681,12 +538,6 @@
     <t>2201382031</t>
   </si>
   <si>
-    <t>2201381988</t>
-  </si>
-  <si>
-    <t>2201381958</t>
-  </si>
-  <si>
     <t>2108438896</t>
   </si>
   <si>
@@ -705,15 +556,6 @@
     <t>0396623386</t>
   </si>
   <si>
-    <t>0379365223</t>
-  </si>
-  <si>
-    <t>0344367477</t>
-  </si>
-  <si>
-    <t>0977995064</t>
-  </si>
-  <si>
     <t>0977602547</t>
   </si>
   <si>
@@ -732,24 +574,6 @@
     <t>0333821793</t>
   </si>
   <si>
-    <t>0984984430</t>
-  </si>
-  <si>
-    <t>0983299045</t>
-  </si>
-  <si>
-    <t>0907071809</t>
-  </si>
-  <si>
-    <t>0523234371</t>
-  </si>
-  <si>
-    <t>0332214383</t>
-  </si>
-  <si>
-    <t>0978425063</t>
-  </si>
-  <si>
     <t>0347335896</t>
   </si>
   <si>
@@ -798,12 +622,6 @@
     <t>0393727443</t>
   </si>
   <si>
-    <t>0359335344</t>
-  </si>
-  <si>
-    <t>0382708626</t>
-  </si>
-  <si>
     <t>0908102473</t>
   </si>
   <si>
@@ -864,12 +682,6 @@
     <t>0944514910</t>
   </si>
   <si>
-    <t>0869899510</t>
-  </si>
-  <si>
-    <t>0344766358</t>
-  </si>
-  <si>
     <t>0969694099</t>
   </si>
   <si>
@@ -882,12 +694,6 @@
     <t>0362730945</t>
   </si>
   <si>
-    <t>0387002882</t>
-  </si>
-  <si>
-    <t>0339896389</t>
-  </si>
-  <si>
     <t>0336316578</t>
   </si>
   <si>
@@ -903,12 +709,6 @@
     <t>0817995224</t>
   </si>
   <si>
-    <t>0377950953</t>
-  </si>
-  <si>
-    <t>0344712627</t>
-  </si>
-  <si>
     <t>0939874120</t>
   </si>
   <si>
@@ -978,9 +778,6 @@
     <t>Làm thuê</t>
   </si>
   <si>
-    <t>Tài xế</t>
-  </si>
-  <si>
     <t>Quân đội</t>
   </si>
   <si>
@@ -1047,12 +844,6 @@
     <t>anh_hs/2_Anh.JPG</t>
   </si>
   <si>
-    <t>anh_hs/3_BAo.JPG</t>
-  </si>
-  <si>
-    <t>anh_hs/4_Binh.JPG</t>
-  </si>
-  <si>
     <t>anh_hs/5_CHuyen.JPG</t>
   </si>
   <si>
@@ -1062,15 +853,6 @@
     <t>anh_hs/7_Dang.JPG</t>
   </si>
   <si>
-    <t>anh_hs/8_Dăng.JPG</t>
-  </si>
-  <si>
-    <t>anh_hs/9_Hao.JPG</t>
-  </si>
-  <si>
-    <t>anh_hs/10_Hien.JPG</t>
-  </si>
-  <si>
     <t>anh_hs/11_Hon.JPG</t>
   </si>
   <si>
@@ -1101,9 +883,6 @@
     <t>anh_hs/20_Lien.JPG</t>
   </si>
   <si>
-    <t>anh_hs/21_Loc.JPG</t>
-  </si>
-  <si>
     <t>anh_hs/22_Nam.JPG</t>
   </si>
   <si>
@@ -1137,9 +916,6 @@
     <t>anh_hs/32_Thai.JPG</t>
   </si>
   <si>
-    <t>anh_hs/33_Thinh.JPG</t>
-  </si>
-  <si>
     <t>anh_hs/34_Tran.JPG</t>
   </si>
   <si>
@@ -1149,9 +925,6 @@
     <t>anh_hs/36_Thu.JPG</t>
   </si>
   <si>
-    <t>anh_hs/37_Tien.JPG</t>
-  </si>
-  <si>
     <t>anh_hs/38_Tram.JPG</t>
   </si>
   <si>
@@ -1159,12 +932,6 @@
   </si>
   <si>
     <t>anh_hs/40_Tuong.JPG</t>
-  </si>
-  <si>
-    <t>anh_hs/41_Vinh.JPG</t>
-  </si>
-  <si>
-    <t>anh_hs/42_Vu.JPG</t>
   </si>
   <si>
     <t>anh_hs/43_VY.JPG</t>
@@ -1185,8 +952,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1240,25 +1007,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 3" xfId="1"/>
+    <cellStyle name="Normal 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1481,23 +1248,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P35"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="12.6328125" style="2"/>
-    <col min="5" max="5" width="18.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" style="2" customWidth="1"/>
-    <col min="7" max="13" width="12.6328125" style="2"/>
-    <col min="14" max="14" width="22.26953125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.6328125" style="6"/>
+    <col min="1" max="1" width="24.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="92.90625" style="6" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="12.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1514,7 +1290,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>312</v>
+        <v>245</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -1523,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>246</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -1535,2070 +1311,1609 @@
         <v>9</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>250</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>317</v>
+        <v>250</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>301</v>
+        <v>234</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>340</v>
+        <v>272</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>384</v>
+        <v>306</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>318</v>
+        <v>251</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>318</v>
+        <v>251</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>303</v>
+        <v>236</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>341</v>
+        <v>273</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>300</v>
+        <v>238</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>342</v>
+        <v>274</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="K6" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="H7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>302</v>
+      <c r="K7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>346</v>
+        <v>278</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="N9" s="2" t="s">
-        <v>347</v>
+        <v>279</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>323</v>
+        <v>255</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>323</v>
+        <v>255</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>348</v>
+        <v>280</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>317</v>
+        <v>256</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>241</v>
+        <v>191</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="L11" s="2" t="s">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>349</v>
+        <v>281</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>324</v>
+        <v>257</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>256</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>244</v>
+        <v>194</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>306</v>
+        <v>236</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>350</v>
+        <v>282</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G13" s="3"/>
+        <v>258</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="H13" s="2" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>318</v>
+        <v>253</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>245</v>
+        <v>196</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>303</v>
+        <v>233</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>351</v>
+        <v>283</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>321</v>
+        <v>251</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>246</v>
+        <v>197</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>306</v>
+        <v>233</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>352</v>
+        <v>284</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>309</v>
+        <v>242</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>304</v>
+        <v>234</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>353</v>
+        <v>285</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>250</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="2" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>301</v>
+        <v>234</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>252</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="2" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>303</v>
+        <v>236</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>326</v>
+        <v>256</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>321</v>
+        <v>256</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>356</v>
+        <v>288</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>337</v>
+        <v>250</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>357</v>
+        <v>289</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>235</v>
+        <v>250</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>206</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>358</v>
+        <v>290</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G21" s="3"/>
+        <v>261</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="H21" s="2" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>327</v>
+        <v>261</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>258</v>
+        <v>208</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>323</v>
+        <v>262</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>259</v>
+        <v>209</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>323</v>
+        <v>262</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>308</v>
+        <v>240</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>360</v>
+        <v>292</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>201</v>
+        <v>161</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="G23" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="H23" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>261</v>
+        <v>250</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>361</v>
+        <v>293</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>307</v>
+        <v>241</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>264</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>215</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>300</v>
+        <v>236</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>363</v>
+        <v>295</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>267</v>
+        <v>256</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>300</v>
+        <v>238</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>364</v>
+        <v>296</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>268</v>
+        <v>250</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>269</v>
+        <v>250</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>365</v>
+        <v>297</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>270</v>
+        <v>218</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>271</v>
+        <v>250</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>366</v>
+        <v>298</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>164</v>
+        <v>127</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>272</v>
+        <v>220</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>317</v>
+        <v>250</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>273</v>
+        <v>221</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>367</v>
+        <v>299</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>322</v>
+        <v>264</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>274</v>
+        <v>222</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>275</v>
+        <v>223</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>308</v>
+        <v>236</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>368</v>
+        <v>300</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>330</v>
+        <v>265</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="2" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>276</v>
+        <v>271</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>303</v>
+        <v>240</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>369</v>
+        <v>301</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>331</v>
+        <v>262</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>305</v>
+        <v>243</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="M32" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="N32" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="O32" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>279</v>
+        <v>266</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>227</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>280</v>
+        <v>266</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="15.75" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>317</v>
+        <v>253</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>281</v>
+        <v>229</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>282</v>
+        <v>253</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>308</v>
+        <v>236</v>
       </c>
       <c r="L34" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="N34" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="O34" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="15.75" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>280</v>
+        <v>269</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>309</v>
+        <v>240</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>373</v>
+        <v>305</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="O37" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="G39" s="3"/>
-      <c r="H39" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="O39" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="G42" s="3"/>
-      <c r="H42" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G43" s="3"/>
-      <c r="H43" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>316</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J17:J32 J36:J45">
-    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q35">
+    <sortCondition ref="Q2:Q35"/>
+  </sortState>
+  <conditionalFormatting sqref="J8:J23 J27:J35">
+    <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
